--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -811,766 +811,766 @@
     <t>0,0,1,1</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.0234,0.0825,0.0077,0.9672</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.1013,0.0010,0.0004,0.9213</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9822,0.0019,0.0003,0.0058</t>
-  </si>
-  <si>
-    <t>0.9864,0.0020,0.0003,0.0036</t>
-  </si>
-  <si>
-    <t>0.9838,0.0013,0.0001,0.0047</t>
-  </si>
-  <si>
-    <t>0.9958,0.0006,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9945,0.0025,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9964,0.0012,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9921,0.0017,0.0005,0.0020</t>
-  </si>
-  <si>
-    <t>0.9964,0.0006,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.2676,0.1688,0.1117,0.4620</t>
-  </si>
-  <si>
-    <t>0.1012,0.0031,0.8556,0.0453</t>
-  </si>
-  <si>
-    <t>0.4913,0.0089,0.5307,0.0223</t>
-  </si>
-  <si>
-    <t>0.0211,0.0167,0.8529,0.2476</t>
-  </si>
-  <si>
-    <t>0.0183,0.0028,0.0028,0.9835</t>
-  </si>
-  <si>
-    <t>0.0007,0.9959,0.0015,0.0049</t>
-  </si>
-  <si>
-    <t>0.0495,0.9385,0.0136,0.0026</t>
-  </si>
-  <si>
-    <t>0.0235,0.9149,0.0098,0.1610</t>
-  </si>
-  <si>
-    <t>0.0054,0.9847,0.0033,0.0086</t>
-  </si>
-  <si>
-    <t>0.0013,0.9956,0.0029,0.0009</t>
-  </si>
-  <si>
-    <t>0.0036,0.0116,0.0078,0.9937</t>
-  </si>
-  <si>
-    <t>0.1077,0.0166,0.2710,0.6602</t>
-  </si>
-  <si>
-    <t>0.0109,0.0014,0.9445,0.0908</t>
-  </si>
-  <si>
-    <t>0.0132,0.0025,0.1952,0.9195</t>
-  </si>
-  <si>
-    <t>0.0339,0.0054,0.9295,0.0539</t>
-  </si>
-  <si>
-    <t>0.0121,0.0012,0.2966,0.8754</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.6485,0.9377</t>
-  </si>
-  <si>
-    <t>0.1127,0.8075,0.0272,0.0595</t>
-  </si>
-  <si>
-    <t>0.4457,0.2668,0.2111,0.0768</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9923,0.1302</t>
-  </si>
-  <si>
-    <t>0.1208,0.6640,0.2105,0.0094</t>
-  </si>
-  <si>
-    <t>0.6645,0.0410,0.0113,0.1569</t>
-  </si>
-  <si>
-    <t>0.1314,0.3769,0.1310,0.5942</t>
-  </si>
-  <si>
-    <t>0.5184,0.4239,0.0548,0.0178</t>
-  </si>
-  <si>
-    <t>0.0016,0.9767,0.0054,0.2398</t>
-  </si>
-  <si>
-    <t>0.0012,0.0110,0.9892,0.0122</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.7739,0.8220</t>
-  </si>
-  <si>
-    <t>0.0040,0.0355,0.9786,0.0118</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.3322,0.9727</t>
-  </si>
-  <si>
-    <t>0.0148,0.0256,0.9719,0.0062</t>
-  </si>
-  <si>
-    <t>0.0119,0.7458,0.6423,0.0085</t>
-  </si>
-  <si>
-    <t>0.0023,0.0167,0.9895,0.0078</t>
-  </si>
-  <si>
-    <t>0.0010,0.0393,0.0008,0.9980</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.0009,0.0659</t>
-  </si>
-  <si>
-    <t>0.0003,0.9915,0.0032,0.1039</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.0003,0.3272</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9961,0.0158</t>
-  </si>
-  <si>
-    <t>0.0004,0.0021,0.9954,0.0106</t>
-  </si>
-  <si>
-    <t>0.0264,0.0013,0.8568,0.1719</t>
-  </si>
-  <si>
-    <t>0.0068,0.0029,0.7938,0.5693</t>
-  </si>
-  <si>
-    <t>0.0007,0.0015,0.9980,0.0022</t>
-  </si>
-  <si>
-    <t>0.0015,0.0006,0.8889,0.4910</t>
-  </si>
-  <si>
-    <t>0.9788,0.0124,0.0010,0.0018</t>
-  </si>
-  <si>
-    <t>0.9930,0.0011,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.9701,0.0024,0.0003,0.0096</t>
-  </si>
-  <si>
-    <t>0.0008,0.0019,0.9911,0.0432</t>
-  </si>
-  <si>
-    <t>0.9938,0.0022,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9974,0.0009,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9340,0.0273,0.0022,0.0093</t>
-  </si>
-  <si>
-    <t>0.0002,0.6424,0.9899,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0009,0.9907,0.0174</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9857,0.1163</t>
-  </si>
-  <si>
-    <t>0.0018,0.0503,0.9932,0.0008</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.9923,0.0525</t>
-  </si>
-  <si>
-    <t>0.0009,0.9950,0.0027,0.0044</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.2437,0.1131,0.0387,0.6186</t>
-  </si>
-  <si>
-    <t>0.8101,0.0502,0.0980,0.0262</t>
-  </si>
-  <si>
-    <t>0.0040,0.0095,0.9812,0.0370</t>
-  </si>
-  <si>
-    <t>0.0024,0.6567,0.9468,0.0004</t>
-  </si>
-  <si>
-    <t>0.0048,0.2843,0.9735,0.0008</t>
-  </si>
-  <si>
-    <t>0.0048,0.7818,0.8101,0.0014</t>
-  </si>
-  <si>
-    <t>0.0001,0.8906,0.9560,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0000,0.9999</t>
+    <t>0.1752,0.1107,0.0168,0.7363</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0273,0.0010,0.0003,0.9792</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9887,0.0005,0.0001,0.0045</t>
+  </si>
+  <si>
+    <t>0.9958,0.0007,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9900,0.0008,0.0001,0.0031</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9944,0.0019,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9961,0.0011,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9916,0.0009,0.0002,0.0028</t>
+  </si>
+  <si>
+    <t>0.9921,0.0007,0.0001,0.0023</t>
+  </si>
+  <si>
+    <t>0.7831,0.0263,0.1317,0.0483</t>
+  </si>
+  <si>
+    <t>0.0471,0.0152,0.4513,0.6882</t>
+  </si>
+  <si>
+    <t>0.3534,0.0065,0.5503,0.0876</t>
+  </si>
+  <si>
+    <t>0.0420,0.0079,0.8024,0.2577</t>
+  </si>
+  <si>
+    <t>0.8665,0.0063,0.0252,0.0558</t>
+  </si>
+  <si>
+    <t>0.0014,0.9944,0.0028,0.0029</t>
+  </si>
+  <si>
+    <t>0.0106,0.9749,0.0068,0.0094</t>
+  </si>
+  <si>
+    <t>0.0435,0.9014,0.0109,0.0758</t>
+  </si>
+  <si>
+    <t>0.0052,0.9837,0.0039,0.0120</t>
+  </si>
+  <si>
+    <t>0.0004,0.9979,0.0011,0.0014</t>
+  </si>
+  <si>
+    <t>0.0225,0.0097,0.0268,0.9665</t>
+  </si>
+  <si>
+    <t>0.1400,0.0029,0.2772,0.5594</t>
+  </si>
+  <si>
+    <t>0.0026,0.0011,0.9667,0.1366</t>
+  </si>
+  <si>
+    <t>0.1290,0.0037,0.1114,0.7668</t>
+  </si>
+  <si>
+    <t>0.0342,0.0021,0.9606,0.0096</t>
+  </si>
+  <si>
+    <t>0.0474,0.0012,0.5943,0.3663</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.8873,0.8501</t>
+  </si>
+  <si>
+    <t>0.0894,0.8738,0.0204,0.0152</t>
+  </si>
+  <si>
+    <t>0.3418,0.3471,0.1835,0.1086</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9966,0.0882</t>
+  </si>
+  <si>
+    <t>0.1155,0.5313,0.3100,0.0518</t>
+  </si>
+  <si>
+    <t>0.1616,0.3371,0.0153,0.5588</t>
+  </si>
+  <si>
+    <t>0.1824,0.4511,0.1239,0.4179</t>
+  </si>
+  <si>
+    <t>0.1448,0.7354,0.0188,0.1040</t>
+  </si>
+  <si>
+    <t>0.0040,0.9640,0.0102,0.2009</t>
+  </si>
+  <si>
+    <t>0.0048,0.1176,0.9628,0.0087</t>
+  </si>
+  <si>
+    <t>0.0009,0.0012,0.9080,0.4642</t>
+  </si>
+  <si>
+    <t>0.0012,0.0070,0.9801,0.0450</t>
+  </si>
+  <si>
+    <t>0.0011,0.0005,0.7274,0.7994</t>
+  </si>
+  <si>
+    <t>0.0097,0.0036,0.9842,0.0046</t>
+  </si>
+  <si>
+    <t>0.0026,0.9145,0.4847,0.0035</t>
+  </si>
+  <si>
+    <t>0.0038,0.0400,0.9761,0.0143</t>
+  </si>
+  <si>
+    <t>0.0002,0.1488,0.0005,0.9989</t>
+  </si>
+  <si>
+    <t>0.0001,0.9956,0.0042,0.0271</t>
+  </si>
+  <si>
+    <t>0.0003,0.9845,0.0025,0.4377</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.0001,0.8428</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9962,0.0177</t>
+  </si>
+  <si>
+    <t>0.0007,0.0027,0.9867,0.0443</t>
+  </si>
+  <si>
+    <t>0.0187,0.0014,0.8684,0.2155</t>
+  </si>
+  <si>
+    <t>0.0117,0.0013,0.8249,0.4285</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9971,0.0038</t>
+  </si>
+  <si>
+    <t>0.0006,0.0006,0.9500,0.3833</t>
+  </si>
+  <si>
+    <t>0.8558,0.0655,0.0031,0.0162</t>
+  </si>
+  <si>
+    <t>0.9868,0.0018,0.0004,0.0038</t>
+  </si>
+  <si>
+    <t>0.9840,0.0012,0.0002,0.0059</t>
+  </si>
+  <si>
+    <t>0.0007,0.0024,0.9918,0.0438</t>
+  </si>
+  <si>
+    <t>0.9810,0.0047,0.0008,0.0040</t>
+  </si>
+  <si>
+    <t>0.9899,0.0050,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.6021,0.2085,0.0032,0.0408</t>
+  </si>
+  <si>
+    <t>0.0004,0.4563,0.9906,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9943,0.0214</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9795,0.1455</t>
+  </si>
+  <si>
+    <t>0.0007,0.3770,0.9886,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0011,0.9938,0.0210</t>
+  </si>
+  <si>
+    <t>0.0040,0.9886,0.0045,0.0034</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.8807,0.0244,0.0274,0.0332</t>
+  </si>
+  <si>
+    <t>0.4985,0.1557,0.1178,0.1675</t>
+  </si>
+  <si>
+    <t>0.0022,0.0059,0.9917,0.0143</t>
+  </si>
+  <si>
+    <t>0.0034,0.1638,0.9836,0.0008</t>
+  </si>
+  <si>
+    <t>0.0059,0.0764,0.9816,0.0031</t>
+  </si>
+  <si>
+    <t>0.0037,0.7623,0.8476,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.9380,0.9113,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.0000,0.9994</t>
   </si>
   <si>
     <t>0.0000,0.0003,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0002,0.0000,0.9999</t>
+    <t>0.0000,0.0007,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0028,0.0008,0.0002,0.9977</t>
+  </si>
+  <si>
+    <t>0.0011,0.0006,0.0000,0.9991</t>
   </si>
   <si>
     <t>0.0000,0.0004,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0114,0.3095,0.9351,0.0032</t>
-  </si>
-  <si>
-    <t>0.0007,0.0500,0.9959,0.0008</t>
-  </si>
-  <si>
-    <t>0.0028,0.0138,0.9919,0.0035</t>
-  </si>
-  <si>
-    <t>0.0009,0.0130,0.9951,0.0029</t>
-  </si>
-  <si>
-    <t>0.0033,0.1702,0.9873,0.0005</t>
-  </si>
-  <si>
-    <t>0.0078,0.0996,0.9556,0.0139</t>
-  </si>
-  <si>
-    <t>0.9963,0.0011,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9934,0.0047,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9794,0.0096,0.0008,0.0025</t>
-  </si>
-  <si>
-    <t>0.9752,0.0032,0.0004,0.0064</t>
-  </si>
-  <si>
-    <t>0.9885,0.0079,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9947,0.0010,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9963,0.0009,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9936,0.0007,0.0001,0.0019</t>
-  </si>
-  <si>
-    <t>0.9938,0.0008,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.9969,0.0003,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9961,0.0005,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9946,0.0021,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9952,0.0010,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9944,0.0004,0.0001,0.0018</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9991,0.0092</t>
-  </si>
-  <si>
-    <t>0.0056,0.0014,0.9487,0.1111</t>
-  </si>
-  <si>
-    <t>0.8393,0.0112,0.1022,0.0335</t>
-  </si>
-  <si>
-    <t>0.0510,0.0024,0.7119,0.2810</t>
-  </si>
-  <si>
-    <t>0.0287,0.9604,0.0079,0.0027</t>
-  </si>
-  <si>
-    <t>0.0288,0.9625,0.0071,0.0014</t>
-  </si>
-  <si>
-    <t>0.0074,0.9744,0.0050,0.0311</t>
-  </si>
-  <si>
-    <t>0.0151,0.9053,0.0137,0.3986</t>
-  </si>
-  <si>
-    <t>0.0203,0.9654,0.0084,0.0054</t>
-  </si>
-  <si>
-    <t>0.0003,0.9976,0.0012,0.0030</t>
-  </si>
-  <si>
-    <t>0.1801,0.7722,0.0185,0.0351</t>
-  </si>
-  <si>
-    <t>0.6836,0.0160,0.2334,0.0904</t>
-  </si>
-  <si>
-    <t>0.0411,0.0049,0.4087,0.7008</t>
-  </si>
-  <si>
-    <t>0.5444,0.0927,0.3284,0.0373</t>
-  </si>
-  <si>
-    <t>0.1445,0.0377,0.1687,0.7203</t>
-  </si>
-  <si>
-    <t>0.0005,0.0366,0.0009,0.9988</t>
-  </si>
-  <si>
-    <t>0.0001,0.9983,0.0031,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0001,0.0968</t>
-  </si>
-  <si>
-    <t>0.0000,0.9966,0.0001,0.8290</t>
-  </si>
-  <si>
-    <t>0.0000,0.9849,0.7795,0.0000</t>
-  </si>
-  <si>
-    <t>0.0247,0.9633,0.0118,0.0012</t>
-  </si>
-  <si>
-    <t>0.1761,0.7812,0.0191,0.0308</t>
-  </si>
-  <si>
-    <t>0.0831,0.8761,0.0130,0.0341</t>
-  </si>
-  <si>
-    <t>0.8943,0.0876,0.0147,0.0065</t>
-  </si>
-  <si>
-    <t>0.9868,0.0011,0.0005,0.0056</t>
-  </si>
-  <si>
-    <t>0.9947,0.0012,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9775,0.0086,0.0024,0.0040</t>
-  </si>
-  <si>
-    <t>0.9961,0.0008,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9605,0.0061,0.0009,0.0115</t>
-  </si>
-  <si>
-    <t>0.9235,0.0009,0.0001,0.0468</t>
-  </si>
-  <si>
-    <t>0.9888,0.0003,0.0001,0.0054</t>
-  </si>
-  <si>
-    <t>0.0040,0.2335,0.9667,0.0020</t>
-  </si>
-  <si>
-    <t>0.0027,0.0247,0.9945,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.0014,0.9953,0.0076</t>
-  </si>
-  <si>
-    <t>0.0069,0.0036,0.9495,0.1140</t>
-  </si>
-  <si>
-    <t>0.1936,0.0259,0.0598,0.7343</t>
-  </si>
-  <si>
-    <t>0.6294,0.0413,0.2356,0.1185</t>
-  </si>
-  <si>
-    <t>0.1503,0.0018,0.4030,0.3679</t>
-  </si>
-  <si>
-    <t>0.0692,0.1236,0.0299,0.8867</t>
-  </si>
-  <si>
-    <t>0.0024,0.0003,0.0000,0.9983</t>
+    <t>0.0012,0.6245,0.9652,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0393,0.9965,0.0009</t>
+  </si>
+  <si>
+    <t>0.0032,0.0409,0.9911,0.0015</t>
+  </si>
+  <si>
+    <t>0.0020,0.0735,0.9891,0.0023</t>
+  </si>
+  <si>
+    <t>0.0018,0.0875,0.9941,0.0005</t>
+  </si>
+  <si>
+    <t>0.0062,0.2418,0.9593,0.0031</t>
+  </si>
+  <si>
+    <t>0.9915,0.0014,0.0002,0.0019</t>
+  </si>
+  <si>
+    <t>0.9960,0.0017,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9809,0.0124,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.9913,0.0037,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9918,0.0026,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9891,0.0014,0.0002,0.0030</t>
+  </si>
+  <si>
+    <t>0.9910,0.0015,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.9777,0.0098,0.0011,0.0030</t>
+  </si>
+  <si>
+    <t>0.9960,0.0007,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9973,0.0009,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9883,0.0005,0.0001,0.0048</t>
+  </si>
+  <si>
+    <t>0.9880,0.0010,0.0001,0.0034</t>
+  </si>
+  <si>
+    <t>0.9964,0.0009,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9951,0.0005,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9978,0.0118</t>
+  </si>
+  <si>
+    <t>0.0188,0.0017,0.8400,0.2308</t>
+  </si>
+  <si>
+    <t>0.4718,0.0898,0.1384,0.2341</t>
+  </si>
+  <si>
+    <t>0.0216,0.0086,0.1931,0.8983</t>
+  </si>
+  <si>
+    <t>0.0198,0.9686,0.0065,0.0037</t>
+  </si>
+  <si>
+    <t>0.0152,0.9774,0.0051,0.0009</t>
+  </si>
+  <si>
+    <t>0.0107,0.9687,0.0062,0.0280</t>
+  </si>
+  <si>
+    <t>0.0044,0.9501,0.0070,0.4205</t>
+  </si>
+  <si>
+    <t>0.0495,0.9230,0.0176,0.0139</t>
+  </si>
+  <si>
+    <t>0.0018,0.9950,0.0020,0.0009</t>
+  </si>
+  <si>
+    <t>0.0880,0.8912,0.0095,0.0136</t>
+  </si>
+  <si>
+    <t>0.0556,0.1555,0.0395,0.9080</t>
+  </si>
+  <si>
+    <t>0.1063,0.0055,0.5941,0.3325</t>
+  </si>
+  <si>
+    <t>0.6657,0.0161,0.0834,0.1475</t>
+  </si>
+  <si>
+    <t>0.3106,0.0402,0.2629,0.3721</t>
+  </si>
+  <si>
+    <t>0.0004,0.0402,0.0012,0.9988</t>
+  </si>
+  <si>
+    <t>0.0001,0.9981,0.0022,0.0046</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.0001,0.4301</t>
+  </si>
+  <si>
+    <t>0.0000,0.9867,0.0002,0.9340</t>
+  </si>
+  <si>
+    <t>0.0001,0.9837,0.7994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0312,0.9565,0.0122,0.0004</t>
+  </si>
+  <si>
+    <t>0.3041,0.6820,0.0237,0.0125</t>
+  </si>
+  <si>
+    <t>0.0942,0.8757,0.0118,0.0220</t>
+  </si>
+  <si>
+    <t>0.8771,0.1097,0.0121,0.0073</t>
+  </si>
+  <si>
+    <t>0.9917,0.0010,0.0002,0.0026</t>
+  </si>
+  <si>
+    <t>0.9708,0.0015,0.0002,0.0114</t>
+  </si>
+  <si>
+    <t>0.8135,0.0053,0.0013,0.1133</t>
+  </si>
+  <si>
+    <t>0.9873,0.0006,0.0001,0.0050</t>
+  </si>
+  <si>
+    <t>0.9445,0.0046,0.0006,0.0192</t>
+  </si>
+  <si>
+    <t>0.9971,0.0006,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.7910,0.0011,0.0001,0.1626</t>
+  </si>
+  <si>
+    <t>0.0017,0.0999,0.9881,0.0015</t>
+  </si>
+  <si>
+    <t>0.0012,0.0483,0.9962,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.0012,0.9881,0.0307</t>
+  </si>
+  <si>
+    <t>0.0034,0.0042,0.9525,0.1487</t>
+  </si>
+  <si>
+    <t>0.1671,0.1351,0.1058,0.6719</t>
+  </si>
+  <si>
+    <t>0.3700,0.0897,0.3799,0.1970</t>
+  </si>
+  <si>
+    <t>0.1844,0.0013,0.4562,0.2593</t>
+  </si>
+  <si>
+    <t>0.8436,0.0085,0.1048,0.0291</t>
+  </si>
+  <si>
+    <t>0.0249,0.0007,0.0001,0.9821</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0006,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.8305,0.9647,0.0001</t>
-  </si>
-  <si>
-    <t>0.9856,0.0018,0.0003,0.0041</t>
-  </si>
-  <si>
-    <t>0.1008,0.8031,0.0249,0.1185</t>
-  </si>
-  <si>
-    <t>0.9866,0.0010,0.0004,0.0054</t>
-  </si>
-  <si>
-    <t>0.5095,0.4795,0.0348,0.0077</t>
-  </si>
-  <si>
-    <t>0.8038,0.0006,0.0001,0.1854</t>
-  </si>
-  <si>
-    <t>0.0025,0.0068,0.0002,0.9972</t>
-  </si>
-  <si>
-    <t>0.9971,0.0005,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.0084,0.0282,0.9959</t>
-  </si>
-  <si>
-    <t>0.2890,0.0020,0.0008,0.7489</t>
-  </si>
-  <si>
-    <t>0.7146,0.0015,0.0005,0.2802</t>
-  </si>
-  <si>
-    <t>0.3710,0.4548,0.1082,0.0193</t>
-  </si>
-  <si>
-    <t>0.5571,0.3508,0.0556,0.0310</t>
-  </si>
-  <si>
-    <t>0.5905,0.3255,0.0446,0.0277</t>
-  </si>
-  <si>
-    <t>0.0619,0.8076,0.0580,0.1528</t>
-  </si>
-  <si>
-    <t>0.9461,0.0180,0.0161,0.0047</t>
-  </si>
-  <si>
-    <t>0.5351,0.2311,0.0244,0.0975</t>
-  </si>
-  <si>
-    <t>0.9770,0.0101,0.0031,0.0032</t>
-  </si>
-  <si>
-    <t>0.9890,0.0016,0.0003,0.0031</t>
-  </si>
-  <si>
-    <t>0.9870,0.0011,0.0004,0.0051</t>
-  </si>
-  <si>
-    <t>0.4758,0.0013,0.0003,0.5310</t>
-  </si>
-  <si>
-    <t>0.9957,0.0014,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9945,0.0010,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9864,0.0004,0.0001,0.0063</t>
-  </si>
-  <si>
-    <t>0.9862,0.0010,0.0004,0.0062</t>
-  </si>
-  <si>
-    <t>0.0834,0.8815,0.0169,0.0251</t>
-  </si>
-  <si>
-    <t>0.4543,0.3158,0.0204,0.1068</t>
-  </si>
-  <si>
-    <t>0.1605,0.7893,0.0307,0.0200</t>
-  </si>
-  <si>
-    <t>0.1449,0.3191,0.0087,0.5362</t>
-  </si>
-  <si>
-    <t>0.8453,0.1425,0.0073,0.0085</t>
-  </si>
-  <si>
-    <t>0.4581,0.4859,0.0229,0.0320</t>
-  </si>
-  <si>
-    <t>0.9886,0.0065,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.9061,0.0650,0.0019,0.0064</t>
-  </si>
-  <si>
-    <t>0.0006,0.0011,0.9787,0.1923</t>
-  </si>
-  <si>
-    <t>0.9729,0.0083,0.0008,0.0044</t>
-  </si>
-  <si>
-    <t>0.0008,0.0005,0.9929,0.0234</t>
-  </si>
-  <si>
-    <t>0.0010,0.0007,0.9953,0.0088</t>
-  </si>
-  <si>
-    <t>0.3029,0.0029,0.4268,0.1656</t>
-  </si>
-  <si>
-    <t>0.0033,0.0029,0.9414,0.2447</t>
-  </si>
-  <si>
-    <t>0.0012,0.0013,0.9854,0.0655</t>
-  </si>
-  <si>
-    <t>0.0032,0.0010,0.9604,0.1596</t>
-  </si>
-  <si>
-    <t>0.0151,0.0018,0.9622,0.0351</t>
-  </si>
-  <si>
-    <t>0.2997,0.0254,0.5536,0.1368</t>
-  </si>
-  <si>
-    <t>0.1490,0.0262,0.2345,0.6299</t>
-  </si>
-  <si>
-    <t>0.2286,0.0085,0.0254,0.7439</t>
-  </si>
-  <si>
-    <t>0.6064,0.0408,0.3507,0.0256</t>
-  </si>
-  <si>
-    <t>0.3921,0.0544,0.4753,0.1098</t>
-  </si>
-  <si>
-    <t>0.5604,0.0347,0.4235,0.0452</t>
-  </si>
-  <si>
-    <t>0.7805,0.0295,0.1742,0.0348</t>
-  </si>
-  <si>
-    <t>0.1800,0.0776,0.1945,0.6431</t>
-  </si>
-  <si>
-    <t>0.6179,0.3615,0.0280,0.0195</t>
-  </si>
-  <si>
-    <t>0.4404,0.5065,0.0076,0.0222</t>
-  </si>
-  <si>
-    <t>0.1899,0.5478,0.0115,0.2139</t>
-  </si>
-  <si>
-    <t>0.7975,0.2228,0.0036,0.0045</t>
-  </si>
-  <si>
-    <t>0.9246,0.0998,0.0027,0.0013</t>
-  </si>
-  <si>
-    <t>0.0149,0.5381,0.0185,0.9367</t>
-  </si>
-  <si>
-    <t>0.1898,0.0072,0.0216,0.7969</t>
-  </si>
-  <si>
-    <t>0.0493,0.0106,0.0217,0.9420</t>
-  </si>
-  <si>
-    <t>0.3530,0.0097,0.1009,0.4716</t>
-  </si>
-  <si>
-    <t>0.7623,0.0051,0.0520,0.1307</t>
-  </si>
-  <si>
-    <t>0.0035,0.0014,0.9754,0.0908</t>
-  </si>
-  <si>
-    <t>0.0021,0.0014,0.8188,0.5747</t>
-  </si>
-  <si>
-    <t>0.0192,0.0021,0.9540,0.0301</t>
-  </si>
-  <si>
-    <t>0.0061,0.0036,0.9702,0.0512</t>
-  </si>
-  <si>
-    <t>0.0015,0.0014,0.9459,0.2028</t>
-  </si>
-  <si>
-    <t>0.9927,0.0028,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.9008,0.0087,0.0006,0.0324</t>
-  </si>
-  <si>
-    <t>0.9976,0.0009,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9960,0.0016,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9788,0.0044,0.0003,0.0040</t>
-  </si>
-  <si>
-    <t>0.9787,0.0115,0.0006,0.0021</t>
-  </si>
-  <si>
-    <t>0.9866,0.0006,0.0001,0.0053</t>
-  </si>
-  <si>
-    <t>0.9474,0.0033,0.0009,0.0222</t>
-  </si>
-  <si>
-    <t>0.0232,0.0201,0.6519,0.6704</t>
-  </si>
-  <si>
-    <t>0.4352,0.3617,0.0527,0.1065</t>
-  </si>
-  <si>
-    <t>0.3515,0.0128,0.0031,0.5791</t>
-  </si>
-  <si>
-    <t>0.0021,0.0013,0.9962,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9944,0.0290</t>
-  </si>
-  <si>
-    <t>0.0189,0.1447,0.9205,0.0231</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9989,0.0027</t>
-  </si>
-  <si>
-    <t>0.0161,0.0060,0.9550,0.0378</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9995,0.0010</t>
-  </si>
-  <si>
-    <t>0.0056,0.0062,0.9746,0.0288</t>
-  </si>
-  <si>
-    <t>0.0887,0.0104,0.8640,0.0513</t>
-  </si>
-  <si>
-    <t>0.1314,0.0062,0.0447,0.8374</t>
-  </si>
-  <si>
-    <t>0.1803,0.0552,0.1085,0.6917</t>
-  </si>
-  <si>
-    <t>0.4285,0.0035,0.0072,0.5665</t>
-  </si>
-  <si>
-    <t>0.9538,0.0066,0.0004,0.0093</t>
-  </si>
-  <si>
-    <t>0.9945,0.0020,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9872,0.0010,0.0002,0.0044</t>
-  </si>
-  <si>
-    <t>0.9940,0.0030,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.8849,0.0049,0.0003,0.0407</t>
-  </si>
-  <si>
-    <t>0.9905,0.0041,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.9922,0.0038,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9951,0.0011,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.0179,0.0072,0.9176,0.1082</t>
-  </si>
-  <si>
-    <t>0.0032,0.0660,0.9866,0.0023</t>
-  </si>
-  <si>
-    <t>0.0030,0.0072,0.9922,0.0050</t>
-  </si>
-  <si>
-    <t>0.0415,0.0052,0.9104,0.0621</t>
-  </si>
-  <si>
-    <t>0.0006,0.0006,0.9450,0.3672</t>
-  </si>
-  <si>
-    <t>0.0036,0.0008,0.1494,0.9634</t>
-  </si>
-  <si>
-    <t>0.0151,0.0129,0.5161,0.7395</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9038,0.4127</t>
-  </si>
-  <si>
-    <t>0.1024,0.0042,0.0008,0.9078</t>
-  </si>
-  <si>
-    <t>0.0000,0.0015,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0007,0.0001,0.9993</t>
+    <t>0.0002,0.0004,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0005,0.5316,0.9842,0.0001</t>
+  </si>
+  <si>
+    <t>0.9913,0.0016,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.0105,0.9457,0.0076,0.1832</t>
+  </si>
+  <si>
+    <t>0.9885,0.0009,0.0002,0.0044</t>
+  </si>
+  <si>
+    <t>0.2360,0.7032,0.0378,0.0324</t>
+  </si>
+  <si>
+    <t>0.8016,0.0008,0.0003,0.1892</t>
+  </si>
+  <si>
+    <t>0.0158,0.0214,0.0015,0.9826</t>
+  </si>
+  <si>
+    <t>0.9977,0.0006,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.0012,0.0556,0.9847</t>
+  </si>
+  <si>
+    <t>0.0587,0.0011,0.0003,0.9566</t>
+  </si>
+  <si>
+    <t>0.2398,0.0031,0.0004,0.7645</t>
+  </si>
+  <si>
+    <t>0.1666,0.6595,0.0513,0.1470</t>
+  </si>
+  <si>
+    <t>0.1438,0.6649,0.0380,0.2964</t>
+  </si>
+  <si>
+    <t>0.6478,0.2159,0.0509,0.0435</t>
+  </si>
+  <si>
+    <t>0.0214,0.9017,0.0201,0.2654</t>
+  </si>
+  <si>
+    <t>0.8382,0.0625,0.0699,0.0097</t>
+  </si>
+  <si>
+    <t>0.6394,0.0677,0.0071,0.1316</t>
+  </si>
+  <si>
+    <t>0.9817,0.0020,0.0008,0.0068</t>
+  </si>
+  <si>
+    <t>0.9964,0.0011,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9868,0.0011,0.0004,0.0053</t>
+  </si>
+  <si>
+    <t>0.9635,0.0013,0.0004,0.0205</t>
+  </si>
+  <si>
+    <t>0.9877,0.0018,0.0007,0.0039</t>
+  </si>
+  <si>
+    <t>0.9799,0.0007,0.0001,0.0094</t>
+  </si>
+  <si>
+    <t>0.9958,0.0003,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9781,0.0009,0.0002,0.0098</t>
+  </si>
+  <si>
+    <t>0.0654,0.8976,0.0116,0.0304</t>
+  </si>
+  <si>
+    <t>0.5041,0.4315,0.0266,0.0369</t>
+  </si>
+  <si>
+    <t>0.0873,0.8546,0.0205,0.0590</t>
+  </si>
+  <si>
+    <t>0.3796,0.1184,0.0094,0.2975</t>
+  </si>
+  <si>
+    <t>0.8778,0.0985,0.0052,0.0077</t>
+  </si>
+  <si>
+    <t>0.0915,0.5147,0.0097,0.5372</t>
+  </si>
+  <si>
+    <t>0.9784,0.0079,0.0013,0.0037</t>
+  </si>
+  <si>
+    <t>0.8640,0.1181,0.0078,0.0081</t>
+  </si>
+  <si>
+    <t>0.0008,0.0009,0.9570,0.3154</t>
+  </si>
+  <si>
+    <t>0.9512,0.0307,0.0035,0.0045</t>
+  </si>
+  <si>
+    <t>0.0007,0.0005,0.9959,0.0110</t>
+  </si>
+  <si>
+    <t>0.0025,0.0028,0.9816,0.0401</t>
+  </si>
+  <si>
+    <t>0.0124,0.0040,0.9676,0.0374</t>
+  </si>
+  <si>
+    <t>0.0021,0.0041,0.9667,0.1409</t>
+  </si>
+  <si>
+    <t>0.0046,0.0032,0.9576,0.1405</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9550,0.3852</t>
+  </si>
+  <si>
+    <t>0.0231,0.0018,0.8367,0.2436</t>
+  </si>
+  <si>
+    <t>0.1111,0.0381,0.4836,0.4092</t>
+  </si>
+  <si>
+    <t>0.5861,0.0052,0.3327,0.0651</t>
+  </si>
+  <si>
+    <t>0.3600,0.0173,0.4276,0.2147</t>
+  </si>
+  <si>
+    <t>0.0796,0.1543,0.0513,0.8506</t>
+  </si>
+  <si>
+    <t>0.4277,0.0172,0.5727,0.0240</t>
+  </si>
+  <si>
+    <t>0.3920,0.0215,0.3916,0.2117</t>
+  </si>
+  <si>
+    <t>0.0305,0.1137,0.0143,0.9535</t>
+  </si>
+  <si>
+    <t>0.5294,0.0108,0.2170,0.2061</t>
+  </si>
+  <si>
+    <t>0.7137,0.2889,0.0298,0.0080</t>
+  </si>
+  <si>
+    <t>0.3594,0.6641,0.0109,0.0078</t>
+  </si>
+  <si>
+    <t>0.3300,0.5279,0.0158,0.0762</t>
+  </si>
+  <si>
+    <t>0.8826,0.1381,0.0080,0.0028</t>
+  </si>
+  <si>
+    <t>0.4686,0.4784,0.0059,0.0201</t>
+  </si>
+  <si>
+    <t>0.3115,0.0193,0.0790,0.5759</t>
+  </si>
+  <si>
+    <t>0.2041,0.0175,0.0090,0.7822</t>
+  </si>
+  <si>
+    <t>0.0623,0.0158,0.0205,0.9310</t>
+  </si>
+  <si>
+    <t>0.6042,0.0044,0.1064,0.1892</t>
+  </si>
+  <si>
+    <t>0.6987,0.0036,0.0540,0.1846</t>
+  </si>
+  <si>
+    <t>0.0014,0.0006,0.9935,0.0211</t>
+  </si>
+  <si>
+    <t>0.0023,0.0033,0.9289,0.2451</t>
+  </si>
+  <si>
+    <t>0.0029,0.0129,0.9930,0.0021</t>
+  </si>
+  <si>
+    <t>0.0004,0.0012,0.9886,0.0585</t>
+  </si>
+  <si>
+    <t>0.0014,0.0027,0.9599,0.1416</t>
+  </si>
+  <si>
+    <t>0.9599,0.0040,0.0003,0.0105</t>
+  </si>
+  <si>
+    <t>0.9781,0.0030,0.0005,0.0061</t>
+  </si>
+  <si>
+    <t>0.9946,0.0016,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9965,0.0014,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9885,0.0016,0.0002,0.0029</t>
+  </si>
+  <si>
+    <t>0.9953,0.0017,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9918,0.0005,0.0001,0.0027</t>
+  </si>
+  <si>
+    <t>0.9750,0.0016,0.0002,0.0086</t>
+  </si>
+  <si>
+    <t>0.0290,0.0040,0.7294,0.4741</t>
+  </si>
+  <si>
+    <t>0.8616,0.0562,0.0319,0.0179</t>
+  </si>
+  <si>
+    <t>0.6683,0.0051,0.0014,0.2628</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9984,0.0043</t>
+  </si>
+  <si>
+    <t>0.0006,0.0045,0.9931,0.0146</t>
+  </si>
+  <si>
+    <t>0.0345,0.0390,0.9261,0.0270</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9994,0.0019</t>
+  </si>
+  <si>
+    <t>0.0559,0.0040,0.9186,0.0286</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9995,0.0007</t>
+  </si>
+  <si>
+    <t>0.0028,0.0023,0.9846,0.0269</t>
+  </si>
+  <si>
+    <t>0.0068,0.0075,0.8168,0.5167</t>
+  </si>
+  <si>
+    <t>0.0218,0.0041,0.0731,0.9514</t>
+  </si>
+  <si>
+    <t>0.5362,0.0051,0.0893,0.2746</t>
+  </si>
+  <si>
+    <t>0.6471,0.0039,0.0143,0.2902</t>
+  </si>
+  <si>
+    <t>0.9881,0.0057,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9844,0.0075,0.0014,0.0021</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0009,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9829,0.0047,0.0003,0.0026</t>
+  </si>
+  <si>
+    <t>0.9944,0.0028,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9943,0.0025,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9931,0.0012,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.0269,0.0106,0.9665,0.0045</t>
+  </si>
+  <si>
+    <t>0.0018,0.0019,0.9959,0.0023</t>
+  </si>
+  <si>
+    <t>0.0075,0.0157,0.9704,0.0272</t>
+  </si>
+  <si>
+    <t>0.0903,0.0056,0.8623,0.0503</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.8577,0.6589</t>
+  </si>
+  <si>
+    <t>0.0031,0.0008,0.1330,0.9688</t>
+  </si>
+  <si>
+    <t>0.0128,0.0147,0.4423,0.8176</t>
+  </si>
+  <si>
+    <t>0.0024,0.0009,0.7898,0.6020</t>
+  </si>
+  <si>
+    <t>0.0113,0.0033,0.0002,0.9898</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0008,0.0000,0.9998</t>
   </si>
   <si>
     <t>0.0000,0.0002,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0018,0.0096,0.0004,0.9980</t>
+    <t>0.0047,0.0105,0.0009,0.9949</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1956,7 @@
         <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1970,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1984,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +1998,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2012,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2026,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2040,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2054,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2068,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2082,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2096,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2110,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2124,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2135,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2152,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2166,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2177,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2194,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2208,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2222,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2236,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2250,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2264,7 @@
         <v>260</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2278,7 @@
         <v>260</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2292,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2306,7 @@
         <v>260</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2320,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2331,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2348,7 @@
         <v>264</v>
       </c>
       <c r="D30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2362,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2373,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2390,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2404,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,10 +2415,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2429,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2443,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2474,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2485,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2502,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2513,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2530,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,10 +2541,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2558,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2572,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2586,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2600,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,10 +2611,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2628,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2642,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2656,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2667,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2684,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2698,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2712,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2726,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2740,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2754,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2768,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2782,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2796,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2807,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2824,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2838,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2852,7 @@
         <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2866,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2880,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2894,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2905,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2919,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2936,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2947,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2964,7 @@
         <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2978,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2992,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3006,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3020,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3034,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3048,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3062,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>269</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3076,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3087,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3104,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3118,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3132,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3146,7 @@
         <v>261</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3160,7 @@
         <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3174,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3188,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3230,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3244,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3258,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3272,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3286,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3300,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3314,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3328,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3342,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3356,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3370,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3384,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3398,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3412,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3423,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3437,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3454,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3468,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3482,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3496,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3510,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3524,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3538,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3549,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3563,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3580,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3591,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3608,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3622,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3636,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3647,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3664,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3678,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3692,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3706,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3720,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3734,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3748,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3762,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3776,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3790,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3804,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3818,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3832,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3846,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3860,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3874,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3888,7 @@
         <v>260</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3899,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3913,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3927,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3944,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3958,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3972,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>347</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>415</v>
@@ -4137,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D158" t="s">
         <v>421</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>422</v>
@@ -4165,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D160" t="s">
         <v>423</v>
@@ -4277,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="C168" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D168" t="s">
         <v>431</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D176" t="s">
         <v>439</v>
@@ -4417,7 +4417,7 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D178" t="s">
         <v>441</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>448</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D190" t="s">
         <v>453</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
         <v>454</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D192" t="s">
         <v>455</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D193" t="s">
         <v>456</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>457</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D195" t="s">
         <v>458</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D196" t="s">
         <v>459</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
         <v>460</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D202" t="s">
         <v>465</v>
@@ -4767,7 +4767,7 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D203" t="s">
         <v>466</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>472</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>484</v>
@@ -5047,7 +5047,7 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
         <v>486</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D231" t="s">
         <v>494</v>
@@ -5187,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
         <v>496</v>
@@ -5201,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D234" t="s">
         <v>497</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D247" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D249" t="s">
         <v>512</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D250" t="s">
         <v>513</v>
@@ -5484,7 +5484,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>409</v>
       </c>
     </row>
     <row r="255" spans="1:4">
